--- a/stories/arbres/ATOM-SAN.HYG.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Baptiste rentre du jardin. Ses mains sentent la terre. Il va aux toilettes. Papa l'attend dans le couloir. Papa dit : après les toilettes, on lave les mains. Baptiste ouvre l'eau. L'eau est tiède. Il prend le savon. Le savon sent la pomme. Il frotte ses mains. Il rince. Il essuie sur la serviette. Les mains sont propres. C'est l'heure de manger. Avant de manger, Baptiste retourne au lavabo. Il ouvre l'eau. Il prend le savon. Il frotte. Il rince. Il essuie. Papa dit : savon et eau. Baptiste sourit. Il s'assoit à table. La soupe est chaude. Papa pose une cuillère. Baptiste dit : savon avant de manger. Savon après les toilettes.</t>
+          <t>Baptiste rentre du jardin. Ses mains sentent la terre. Il va aux toilettes. Papa l'attend dans le couloir. Après les toilettes, on lave les mains. Baptiste ouvre l'eau. L'eau est tiède. Il prend le savon. Le savon sent la pomme. Il frotte ses mains. Il rince. Il essuie sur la serviette. Les mains sont propres. C'est l'heure de manger. Avant de manger, Baptiste retourne au lavabo. Il ouvre l'eau. Il prend le savon. Il frotte. Il rince. Il essuie. Savon et eau. Baptiste sourit. Il s'assoit à table. La soupe est chaude. Papa pose une cuillère. Savon avant de manger. Savon après les toilettes.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Baptiste rentre du jardin. Ses mains sentent la terre. Il va aux toilettes. Papa l'attend dans le couloir.
+papa|Après les toilettes, on lave les mains.
+narrateur|Baptiste ouvre l'eau. L'eau est tiède. Il prend le savon. Le savon sent la pomme. Il frotte ses mains. Il rince. Il essuie sur la serviette. Les mains sont propres. C'est l'heure de manger. Avant de manger, Baptiste retourne au lavabo. Il ouvre l'eau. Il prend le savon. Il frotte. Il rince. Il essuie.
+papa|Savon et eau.
+narrateur|Baptiste sourit. Il s'assoit à table. La soupe est chaude. Papa pose une cuillère.
+enfant-m|Savon avant de manger. Savon après les toilettes.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Baptiste se lave les mains. Avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Après les toilettes, Baptiste a lavé. Avant de manger, Baptiste a lavé. Ouvrir l'eau, savon, rincer, essuyer.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1835,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Baptiste s'assoit près de papa. Ses mains sont propres.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2002,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2042,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 enfant-m|Savon avant de manger. Savon après les toilettes.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Baptiste se lave les mains. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1680,7 @@
           <t>narrateur|Après les toilettes, Baptiste a lavé. Avant de manger, Baptiste a lavé. Ouvrir l'eau, savon, rincer, essuyer.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1840,6 +1848,7 @@
           <t>narrateur|Baptiste s'assoit près de papa. Ses mains sont propres.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2007,6 +2016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2049,6 +2059,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2250,6 +2274,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Baptiste lave ses mains</t>
+          <t>La soupe de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'arrosoir goutte dans le jardin. Nino rentre, va aux toilettes, se lave au savon pomme, puis encore avant la soupe chaude.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Baptiste rentre du jardin. Ses mains sentent la terre. Il va aux toilettes. Papa l'attend dans le couloir. Après les toilettes, on lave les mains. Baptiste ouvre l'eau. L'eau est tiède. Il prend le savon. Le savon sent la pomme. Il frotte ses mains. Il rince. Il essuie sur la serviette. Les mains sont propres. C'est l'heure de manger. Avant de manger, Baptiste retourne au lavabo. Il ouvre l'eau. Il prend le savon. Il frotte. Il rince. Il essuie. Savon et eau. Baptiste sourit. Il s'assoit à table. La soupe est chaude. Papa pose une cuillère. Savon avant de manger. Savon après les toilettes.</t>
+          <t>L'arrosoir laisse tomber une perle d'eau. La perle brille sur une feuille. Une petite bête rouge marche tout lentement. La terre sent le jardin mouillé. La porte de bois craque un peu. Les bottes de Nino sont près du paillasson. Un rayon passe dans la cuisine. Nino, rentre. La soupe est presque prête. J'arrive, papa. Tu as vu la petite bête rouge ? Oui. Sur la feuille. En ce moment, Nino rentre du jardin. Ses mains sentent la terre. Il laisse les bottes au paillasson. Il va aux toilettes. Papa l'attend dans le couloir. Après les toilettes, on lave les mains. Savon et eau. Nino ouvre l'eau. L'eau est tiède. Il prend le savon. Le savon sent la pomme. Ça sent la pomme. Oui. Frotte bien. Nino frotte ses mains. Il frotte le dessus. Il frotte le dessous. Il rince. Il essuie sur la serviette. Les mains sont propres. Bravo. Tu as fait du bon travail. Plus de terre. Oui. Tes mains sentent la pomme. La cuisine sent la soupe. La vapeur danse au-dessus de la casserole. C'est l'heure de manger. Avant de manger, on lave. Je retourne au lavabo. Nino ouvre l'eau. Il prend le savon. Il frotte. Il rince. Il essuie. Savon et eau. Tu as fini de laver tes mains ? Oui, papa. Bravo. Assieds-toi. Nino s'assoit à table. La soupe est chaude. Papa pose une cuillère. Savon avant de manger. Savon après les toilettes. Oui. C'est ça.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Baptiste rentre du jardin. Ses mains sentent la terre. Il va aux toilettes. Papa l'attend dans le couloir.
+          <t>narrateur|L'arrosoir laisse tomber une perle d'eau.
+narrateur|La perle brille sur une feuille.
+narrateur|Une petite bête rouge marche tout lentement.
+narrateur|La terre sent le jardin mouillé.
+narrateur|La porte de bois craque un peu.
+narrateur|Les bottes de Nino sont près du paillasson.
+narrateur|Un rayon passe dans la cuisine.
+papa|Nino, rentre. La soupe est presque prête.
+enfant-m|J'arrive, papa.
+papa|Tu as vu la petite bête rouge ?
+enfant-m|Oui. Sur la feuille.
+narrateur|En ce moment, Nino rentre du jardin.
+narrateur|Ses mains sentent la terre.
+narrateur|Il laisse les bottes au paillasson.
+narrateur|Il va aux toilettes.
+narrateur|Papa l'attend dans le couloir.
 papa|Après les toilettes, on lave les mains.
-narrateur|Baptiste ouvre l'eau. L'eau est tiède. Il prend le savon. Le savon sent la pomme. Il frotte ses mains. Il rince. Il essuie sur la serviette. Les mains sont propres. C'est l'heure de manger. Avant de manger, Baptiste retourne au lavabo. Il ouvre l'eau. Il prend le savon. Il frotte. Il rince. Il essuie.
 papa|Savon et eau.
-narrateur|Baptiste sourit. Il s'assoit à table. La soupe est chaude. Papa pose une cuillère.
-enfant-m|Savon avant de manger. Savon après les toilettes.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Nino ouvre l'eau.
+narrateur|L'eau est tiède.
+narrateur|Il prend le savon.
+narrateur|Le savon sent la pomme.
+enfant-m|Ça sent la pomme.
+papa|Oui. Frotte bien.
+narrateur|Nino frotte ses mains.
+narrateur|Il frotte le dessus.
+narrateur|Il frotte le dessous.
+narrateur|Il rince.
+narrateur|Il essuie sur la serviette.
+narrateur|Les mains sont propres.
+papa|Bravo. Tu as fait du bon travail.
+enfant-m|Plus de terre.
+papa|Oui. Tes mains sentent la pomme.
+narrateur|La cuisine sent la soupe.
+narrateur|La vapeur danse au-dessus de la casserole.
+papa|C'est l'heure de manger.
+papa|Avant de manger, on lave.
+enfant-m|Je retourne au lavabo.
+narrateur|Nino ouvre l'eau.
+narrateur|Il prend le savon.
+narrateur|Il frotte. Il rince. Il essuie.
+papa|Savon et eau.
+papa|Tu as fini de laver tes mains ?
+enfant-m|Oui, papa.
+papa|Bravo. Assieds-toi.
+narrateur|Nino s'assoit à table.
+narrateur|La soupe est chaude.
+narrateur|Papa pose une cuillère.
+enfant-m|Savon avant de manger.
+enfant-m|Savon après les toilettes.
+papa|Oui. C'est ça.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Baptiste se lave les mains. Avec quoi ?</t>
+          <t>Nino se lave les mains. Avec quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1505,10 +1561,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Baptiste se lave les mains. Avec quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nino se lave les mains.
+narrateur|Avec quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Après les toilettes, Baptiste a lavé. Avant de manger, Baptiste a lavé. Ouvrir l'eau, savon, rincer, essuyer.</t>
+          <t>Après les toilettes, Nino a lavé. Avant de manger, Nino a lavé. Ouvrir l'eau, savon, rincer, essuyer. Tu te souviens du savon pomme ? Oui. Savon et eau. Bravo. Tes mains sentent la pomme. L'arrosoir est resté dans le jardin. La perle d'eau n'est plus sur la feuille. Les bottes sèchent près de la porte.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1677,10 +1733,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Après les toilettes, Baptiste a lavé. Avant de manger, Baptiste a lavé. Ouvrir l'eau, savon, rincer, essuyer.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Après les toilettes, Nino a lavé.
+narrateur|Avant de manger, Nino a lavé.
+narrateur|Ouvrir l'eau, savon, rincer, essuyer.
+papa|Tu te souviens du savon pomme ?
+enfant-m|Oui. Savon et eau.
+papa|Bravo. Tes mains sentent la pomme.
+narrateur|L'arrosoir est resté dans le jardin.
+narrateur|La perle d'eau n'est plus sur la feuille.
+narrateur|Les bottes sèchent près de la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1705,7 +1768,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Baptiste s'assoit près de papa. Ses mains sont propres.</t>
+          <t>Nino s'assoit près de papa. Ses mains sont propres. La soupe fume un peu. Souffle un peu, elle est chaude. Elle sent bon. Tu as les mains propres pour la cuillère. Oui. Bravo, Nino. La casserole chante tout doucement. Le rayon de lumière touche la table.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1845,10 +1908,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Baptiste s'assoit près de papa. Ses mains sont propres.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nino s'assoit près de papa.
+narrateur|Ses mains sont propres.
+narrateur|La soupe fume un peu.
+papa|Souffle un peu, elle est chaude.
+enfant-m|Elle sent bon.
+papa|Tu as les mains propres pour la cuillère.
+enfant-m|Oui.
+papa|Bravo, Nino.
+narrateur|La casserole chante tout doucement.
+narrateur|Le rayon de lumière touche la table.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1873,7 +1944,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a lavé après les toilettes. Nino a lavé avant de manger. Bravo. C'est du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2013,10 +2084,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Nino a lavé après les toilettes.
+narrateur|Nino a lavé avant de manger.
+papa|Bravo. C'est du bon travail.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2035,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2073,6 +2146,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'arrosoir laisse tomber une perle d'eau. La perle brille sur une feuille. Une petite bête rouge marche tout lentement. La terre sent le jardin mouillé. La porte de bois craque un peu. Les bottes de Nino sont près du paillasson. Un rayon passe dans la cuisine. Nino, rentre. La soupe est presque prête. J'arrive, papa. Tu as vu la petite bête rouge ? Oui. Sur la feuille. En ce moment, Nino rentre du jardin. Ses mains sentent la terre. Il laisse les bottes au paillasson. Il va aux toilettes. Papa l'attend dans le couloir. Après les toilettes, on lave les mains. Savon et eau. Nino ouvre l'eau. L'eau est tiède. Il prend le savon. Le savon sent la pomme. Ça sent la pomme. Oui. Frotte bien. Nino frotte ses mains. Il frotte le dessus. Il frotte le dessous. Il rince. Il essuie sur la serviette. Les mains sont propres. Bravo. Tu as fait du bon travail. Plus de terre. Oui. Tes mains sentent la pomme. La cuisine sent la soupe. La vapeur danse au-dessus de la casserole. C'est l'heure de manger. Avant de manger, on lave. Je retourne au lavabo. Nino ouvre l'eau. Il prend le savon. Il frotte. Il rince. Il essuie. Savon et eau. Tu as fini de laver tes mains ? Oui, papa. Bravo. Assieds-toi. Nino s'assoit à table. La soupe est chaude. Papa pose une cuillère. Savon avant de manger. Savon après les toilettes. Oui. C'est ça.</t>
+          <t>L'arrosoir laisse tomber une perle d'eau. La perle brille sur une feuille. Une petite bête rouge marche tout lentement. La terre sent le jardin mouillé. La porte de bois craque un peu. Les bottes de Nino sont près du paillasson. Un rayon passe dans la cuisine. Nino, rentre. La soupe est presque prête. J'arrive, papa. Tu as vu la petite bête rouge ? Oui. Sur la feuille. En ce moment, Nino rentre du jardin. Ses mains sentent la terre. Il laisse les bottes au paillasson. Il va aux toilettes. Nino rejoint papa dans le couloir. Après les toilettes, on lave les mains. Savon et eau. Nino ouvre l'eau. L'eau est tiède. Il prend le savon. Le savon sent la pomme. Ça sent la pomme. Oui. Frotte bien. Nino frotte ses mains. Il frotte le dessus. Il frotte le dessous. Il rince. Il essuie sur la serviette. Les mains sont propres. Plus de terre. Oui. Tes mains sentent la pomme. Tu as fini de laver tes mains ? Oui, papa. Bravo. La cuisine sent la soupe. La vapeur danse au-dessus de la casserole. C'est l'heure de manger. Avant de manger, on lave. Je retourne au lavabo. Nino ouvre l'eau. Il prend le savon. Il frotte. Il rince. Il essuie. Savon et eau. Tu as fini de laver tes mains ? Oui, papa. Bravo. Assieds-toi. Nino s'assoit à table. La soupe est chaude. Papa pose une cuillère. Savon avant de manger. Savon après les toilettes. Oui. C'est ça.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Baptiste rentre du jardin. Ses mains sentent la terre. Il va aux toilettes. Papa l'attend dans le couloir. Papa dit : après les toilettes, on lave les mains. Baptiste ouvre l'eau. L'eau est tiède. Il prend le &lt;emphasis level="moderate"&gt;savon&lt;/emphasis&gt;. Le savon sent la pomme. Il frotte ses mains. Il rince. Il essuie sur la serviette. Les mains sont propres. C'est l'heure de manger. Avant de manger, Baptiste retourne au lavabo. Il ouvre l'eau. Il prend le savon. Il frotte. Il rince. Il essuie. Papa dit : savon et eau. Baptiste sourit. Il s'assoit à table. La soupe est chaude. Papa pose une cuillère. Baptiste dit : savon avant de manger. Savon après les toilettes.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrosoir laisse tomber une perle d'eau. La perle brille sur une feuille. Une petite bête rouge marche tout lentement. La terre sent le jardin mouillé. La porte de bois craque un peu. Les bottes de Nino sont près du paillasson. Un rayon passe dans la cuisine. Nino, rentre. La soupe est presque prête. J'arrive, papa. Tu as vu la petite bête rouge ? Oui. Sur la feuille. En ce moment, Nino rentre du jardin. Ses mains sentent la terre. Il laisse les bottes au paillasson. Il va aux toilettes. Nino rejoint papa dans le couloir. Après les toilettes, on lave les mains. Savon et eau. Nino ouvre l'eau. L'eau est tiède. Il prend le savon. Le savon sent la pomme. Ça sent la pomme. Oui. Frotte bien. Nino frotte ses mains. Il frotte le dessus. Il frotte le dessous. Il rince. Il essuie sur la serviette. Les mains sont propres. Plus de terre. Oui. Tes mains sentent la pomme. Tu as fini de laver tes mains ? Oui, papa. Bravo. La cuisine sent la soupe. La vapeur danse au-dessus de la casserole. C'est l'heure de manger. Avant de manger, on lave. Je retourne au lavabo. Nino ouvre l'eau. Il prend le savon. Il frotte. Il rince. Il essuie. Savon et eau. Tu as fini de laver tes mains ? Oui, papa. Bravo. Assieds-toi. Nino s'assoit à table. La soupe est chaude. Papa pose une cuillère. Savon avant de manger. Savon après les toilettes. Oui. C'est ça.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
 narrateur|Ses mains sentent la terre.
 narrateur|Il laisse les bottes au paillasson.
 narrateur|Il va aux toilettes.
-narrateur|Papa l'attend dans le couloir.
+narrateur|Nino rejoint papa dans le couloir.
 papa|Après les toilettes, on lave les mains.
 papa|Savon et eau.
 narrateur|Nino ouvre l'eau.
@@ -1354,9 +1354,11 @@
 narrateur|Il rince.
 narrateur|Il essuie sur la serviette.
 narrateur|Les mains sont propres.
-papa|Bravo. Tu as fait du bon travail.
 enfant-m|Plus de terre.
 papa|Oui. Tes mains sentent la pomme.
+papa|Tu as fini de laver tes mains ?
+enfant-m|Oui, papa.
+papa|Bravo.
 narrateur|La cuisine sent la soupe.
 narrateur|La vapeur danse au-dessus de la casserole.
 papa|C'est l'heure de manger.
@@ -1406,7 +1408,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Baptiste se lave les &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s. Avec quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino se lave les mains. Avec quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1594,7 +1596,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après les toilettes, Baptiste a lavé. Avant de manger, Baptiste a lavé. Ouvrir l'eau, &lt;emphasis level="moderate"&gt;savon&lt;/emphasis&gt;, rincer, essuyer.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après les toilettes, Nino a lavé. Avant de manger, Nino a lavé. Ouvrir l'eau, savon, rincer, essuyer. Tu te souviens du savon pomme ? Oui. Savon et eau. Bravo. Tes mains sentent la pomme. L'arrosoir est resté dans le jardin. La perle d'eau n'est plus sur la feuille. Les bottes sèchent près de la porte.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1773,7 +1775,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Baptiste s'assoit près de papa. Ses &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s sont propres.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino s'assoit près de papa. Ses mains sont propres. La soupe fume un peu. Souffle un peu, elle est chaude. Elle sent bon. Tu as les mains propres pour la cuillère. Oui. Bravo, Nino. La casserole chante tout doucement. Le rayon de lumière touche la table.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1944,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nino a lavé après les toilettes. Nino a lavé avant de manger. Bravo. C'est du bon travail. L'histoire est finie.</t>
+          <t>Nino a lavé après les toilettes. Nino a lavé avant de manger.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a lavé après les toilettes. Nino a lavé avant de manger.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2085,9 +2087,7 @@
       <c r="AW6" t="inlineStr">
         <is>
           <t>narrateur|Nino a lavé après les toilettes.
-narrateur|Nino a lavé avant de manger.
-papa|Bravo. C'est du bon travail.
-narrateur|L'histoire est finie.</t>
+narrateur|Nino a lavé avant de manger.</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2153,6 +2153,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison après le jardin</t>
+          <t>jardin puis maison</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Baptiste, papa</t>
+          <t>Nino, papa</t>
         </is>
       </c>
     </row>
